--- a/artfynd/A 19608-2023 artfynd.xlsx
+++ b/artfynd/A 19608-2023 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188820</v>
+        <v>113188821</v>
       </c>
       <c r="B9" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750766</v>
+        <v>750557</v>
       </c>
       <c r="R9" t="n">
-        <v>7215959</v>
+        <v>7216086</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1697,7 +1697,7 @@
         <v>113188823</v>
       </c>
       <c r="B11" t="n">
-        <v>77508</v>
+        <v>77524</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>113188792</v>
       </c>
       <c r="B12" t="n">
-        <v>78697</v>
+        <v>78713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188821</v>
+        <v>113188820</v>
       </c>
       <c r="B13" t="n">
-        <v>78105</v>
+        <v>78121</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750557</v>
+        <v>750766</v>
       </c>
       <c r="R13" t="n">
-        <v>7216086</v>
+        <v>7215959</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 19608-2023 artfynd.xlsx
+++ b/artfynd/A 19608-2023 artfynd.xlsx
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188821</v>
+        <v>113188820</v>
       </c>
       <c r="B9" t="n">
         <v>78121</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750557</v>
+        <v>750766</v>
       </c>
       <c r="R9" t="n">
-        <v>7216086</v>
+        <v>7215959</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188798</v>
+        <v>113188823</v>
       </c>
       <c r="B10" t="n">
-        <v>56910</v>
+        <v>77524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,38 +1594,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750567</v>
+        <v>750688</v>
       </c>
       <c r="R10" t="n">
-        <v>7215982</v>
+        <v>7215922</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1657,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188823</v>
+        <v>113188798</v>
       </c>
       <c r="B11" t="n">
-        <v>77524</v>
+        <v>56910</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,34 +1706,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750688</v>
+        <v>750567</v>
       </c>
       <c r="R11" t="n">
-        <v>7215922</v>
+        <v>7215982</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188792</v>
+        <v>113188821</v>
       </c>
       <c r="B12" t="n">
-        <v>78713</v>
+        <v>78121</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750688</v>
+        <v>750557</v>
       </c>
       <c r="R12" t="n">
-        <v>7215922</v>
+        <v>7216086</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188820</v>
+        <v>113188792</v>
       </c>
       <c r="B13" t="n">
-        <v>78121</v>
+        <v>78713</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750766</v>
+        <v>750688</v>
       </c>
       <c r="R13" t="n">
-        <v>7215959</v>
+        <v>7215922</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 19608-2023 artfynd.xlsx
+++ b/artfynd/A 19608-2023 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188820</v>
+        <v>113188798</v>
       </c>
       <c r="B9" t="n">
-        <v>78121</v>
+        <v>56911</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,34 +1482,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750766</v>
+        <v>750567</v>
       </c>
       <c r="R9" t="n">
-        <v>7215959</v>
+        <v>7215982</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1545,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1555,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1582,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188823</v>
+        <v>113188821</v>
       </c>
       <c r="B10" t="n">
-        <v>77524</v>
+        <v>78133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,21 +1598,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1618,10 +1622,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750688</v>
+        <v>750557</v>
       </c>
       <c r="R10" t="n">
-        <v>7215922</v>
+        <v>7216086</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1694,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188798</v>
+        <v>113188792</v>
       </c>
       <c r="B11" t="n">
-        <v>56910</v>
+        <v>78725</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,38 +1710,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750567</v>
+        <v>750688</v>
       </c>
       <c r="R11" t="n">
-        <v>7215982</v>
+        <v>7215922</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188821</v>
+        <v>113188823</v>
       </c>
       <c r="B12" t="n">
-        <v>78121</v>
+        <v>77536</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,21 +1822,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750557</v>
+        <v>750688</v>
       </c>
       <c r="R12" t="n">
-        <v>7216086</v>
+        <v>7215922</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188792</v>
+        <v>113188820</v>
       </c>
       <c r="B13" t="n">
-        <v>78713</v>
+        <v>78133</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,21 +1934,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750688</v>
+        <v>750766</v>
       </c>
       <c r="R13" t="n">
-        <v>7215922</v>
+        <v>7215959</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 19608-2023 artfynd.xlsx
+++ b/artfynd/A 19608-2023 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188798</v>
+        <v>113188821</v>
       </c>
       <c r="B9" t="n">
-        <v>56911</v>
+        <v>78133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,38 +1482,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750567</v>
+        <v>750557</v>
       </c>
       <c r="R9" t="n">
-        <v>7215982</v>
+        <v>7216086</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1545,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1555,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,7 +1578,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188821</v>
+        <v>113188820</v>
       </c>
       <c r="B10" t="n">
         <v>78133</v>
@@ -1622,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750557</v>
+        <v>750766</v>
       </c>
       <c r="R10" t="n">
-        <v>7216086</v>
+        <v>7215959</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1657,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1667,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188792</v>
+        <v>113188823</v>
       </c>
       <c r="B11" t="n">
-        <v>78725</v>
+        <v>77536</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,21 +1706,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1806,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188823</v>
+        <v>113188792</v>
       </c>
       <c r="B12" t="n">
-        <v>77536</v>
+        <v>78725</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1822,21 +1818,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1918,10 +1914,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188820</v>
+        <v>113188798</v>
       </c>
       <c r="B13" t="n">
-        <v>78133</v>
+        <v>56911</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,34 +1930,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750766</v>
+        <v>750567</v>
       </c>
       <c r="R13" t="n">
-        <v>7215959</v>
+        <v>7215982</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 19608-2023 artfynd.xlsx
+++ b/artfynd/A 19608-2023 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188821</v>
+        <v>113188792</v>
       </c>
       <c r="B9" t="n">
-        <v>78133</v>
+        <v>78747</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750557</v>
+        <v>750688</v>
       </c>
       <c r="R9" t="n">
-        <v>7216086</v>
+        <v>7215922</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
         <v>113188820</v>
       </c>
       <c r="B10" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188823</v>
+        <v>113188821</v>
       </c>
       <c r="B11" t="n">
-        <v>77536</v>
+        <v>78155</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750688</v>
+        <v>750557</v>
       </c>
       <c r="R11" t="n">
-        <v>7215922</v>
+        <v>7216086</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188792</v>
+        <v>113188823</v>
       </c>
       <c r="B12" t="n">
-        <v>78725</v>
+        <v>77558</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>

--- a/artfynd/A 19608-2023 artfynd.xlsx
+++ b/artfynd/A 19608-2023 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113188792</v>
+        <v>113188821</v>
       </c>
       <c r="B9" t="n">
-        <v>78747</v>
+        <v>78158</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,21 +1482,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750688</v>
+        <v>750557</v>
       </c>
       <c r="R9" t="n">
-        <v>7215922</v>
+        <v>7216086</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,7 +1581,7 @@
         <v>113188820</v>
       </c>
       <c r="B10" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113188821</v>
+        <v>113188823</v>
       </c>
       <c r="B11" t="n">
-        <v>78155</v>
+        <v>77561</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,21 +1706,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750557</v>
+        <v>750688</v>
       </c>
       <c r="R11" t="n">
-        <v>7216086</v>
+        <v>7215922</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,10 +1802,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188823</v>
+        <v>113188798</v>
       </c>
       <c r="B12" t="n">
-        <v>77558</v>
+        <v>56914</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,34 +1818,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750688</v>
+        <v>750567</v>
       </c>
       <c r="R12" t="n">
-        <v>7215922</v>
+        <v>7215982</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1877,7 +1881,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1887,7 +1891,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,10 +1918,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113188798</v>
+        <v>113188792</v>
       </c>
       <c r="B13" t="n">
-        <v>56911</v>
+        <v>78751</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1930,38 +1934,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750567</v>
+        <v>750688</v>
       </c>
       <c r="R13" t="n">
-        <v>7215982</v>
+        <v>7215922</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 19608-2023 artfynd.xlsx
+++ b/artfynd/A 19608-2023 artfynd.xlsx
@@ -1469,7 +1469,7 @@
         <v>113188821</v>
       </c>
       <c r="B9" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113188820</v>
+        <v>113188798</v>
       </c>
       <c r="B10" t="n">
-        <v>78158</v>
+        <v>56918</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,34 +1594,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750766</v>
+        <v>750567</v>
       </c>
       <c r="R10" t="n">
-        <v>7215959</v>
+        <v>7215982</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1653,7 +1657,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1667,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1697,7 @@
         <v>113188823</v>
       </c>
       <c r="B11" t="n">
-        <v>77561</v>
+        <v>77567</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1802,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113188798</v>
+        <v>113188820</v>
       </c>
       <c r="B12" t="n">
-        <v>56914</v>
+        <v>78164</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1818,38 +1822,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fjällboheden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750567</v>
+        <v>750766</v>
       </c>
       <c r="R12" t="n">
-        <v>7215982</v>
+        <v>7215959</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,7 +1921,7 @@
         <v>113188792</v>
       </c>
       <c r="B13" t="n">
-        <v>78751</v>
+        <v>78757</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 19608-2023 artfynd.xlsx
+++ b/artfynd/A 19608-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,6 +2028,122 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114729880</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dalslyet, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>750497</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7216022</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-01-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-01-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19608-2023 artfynd.xlsx
+++ b/artfynd/A 19608-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
